--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,9 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -70,6 +73,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -460,92 +472,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Subchapter No</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>English Question</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Assamese Question</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -555,85 +572,86 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>What is 2 + 2?</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2 + 2 কিমান?</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Correct answer is 4.</t>
         </is>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -567,6 +567,11 @@
           <t>Explanation</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Variation Group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -656,6 +661,7 @@
           <t>Correct answer is 4.</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,11 @@
           <t>Variation Group</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Fixed Question</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -661,7 +666,11 @@
           <t>Correct answer is 4.</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -574,6 +574,11 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Lesson / Topic</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>Fixed Question</t>
         </is>
       </c>
@@ -667,6 +672,11 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Example: Addition of Unlike Fractions</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -448,121 +448,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Subchapter No</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>English Question</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Assamese Question</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -582,91 +588,100 @@
           <t>Fixed Question</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Text_Book</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Textbook_Reference</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>What is 2 + 2?</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>2 + 2 কিমান?</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Correct answer is 4.</t>
         </is>
@@ -679,6 +694,16 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NCERT Class 6, Ch 7, Ex 7.1, Q3</t>
         </is>
       </c>
     </row>
@@ -693,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -804,6 +829,42 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mathematics in Excel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Write LaTeX directly in question/option/explanation cells, e.g. \frac{3}{4}, x^2, \sqrt{25}, \times, \div. You may also use $...$ or \(...\). The importer converts it for MathJax rendering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Text_Book</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>YES if the question is taken from the textbook; NO otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Textbook_Reference</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optional source details, e.g. NCERT Class 8, Chapter 3, Exercise 3.2, Question 5, page 62.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -63,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -82,6 +83,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,7 +728,7 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -746,9 +753,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Question Type</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>English Question and Assamese Question belong to the SAME question row. Fill one or both.</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -758,9 +765,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Cognitive Level</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Language is detected automatically: English only → ENGLISH; Assamese only → ASSAMESE; both → BOTH.</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -770,9 +777,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Question Paper Generator: English / Assamese / Both Medium. Both Medium prints both versions under the same serial number.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -782,9 +789,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Do not create separate rows for the English and Assamese versions of the same question.</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Bank Bulk" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Question Bank Bulk'!$A$1:$Z$101</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -39,7 +41,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +53,18 @@
         <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,11 +72,16 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -90,6 +107,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,154 +477,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Subchapter No</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>English Question</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Assamese Question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>Variation Group</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>Lesson / Topic</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>Fixed Question</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>Text_Book</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>Textbook_Reference</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>Image Required</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>Image Description</t>
         </is>
       </c>
     </row>
@@ -713,8 +747,407 @@
           <t>NCERT Class 6, Ch 7, Ex 7.1, Q3</t>
         </is>
       </c>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+    </row>
+    <row r="3">
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+    </row>
+    <row r="4">
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+    </row>
+    <row r="5">
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="Y11" s="10" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="Y20" s="10" t="n"/>
+      <c r="Z20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="Y22" s="10" t="n"/>
+      <c r="Z22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="Y23" s="10" t="n"/>
+      <c r="Z23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="Y24" s="10" t="n"/>
+      <c r="Z24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="Y25" s="10" t="n"/>
+      <c r="Z25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="Y26" s="10" t="n"/>
+      <c r="Z26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="Y27" s="10" t="n"/>
+      <c r="Z27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="Y28" s="10" t="n"/>
+      <c r="Z28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="Y29" s="10" t="n"/>
+      <c r="Z29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="Y30" s="10" t="n"/>
+      <c r="Z30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="Y31" s="10" t="n"/>
+      <c r="Z31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="Y32" s="10" t="n"/>
+      <c r="Z32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="Y33" s="10" t="n"/>
+      <c r="Z33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="Y34" s="10" t="n"/>
+      <c r="Z34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="Y36" s="10" t="n"/>
+      <c r="Z36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="Y37" s="10" t="n"/>
+      <c r="Z37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="Y38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="Y39" s="10" t="n"/>
+      <c r="Z39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="Y40" s="10" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="Y41" s="10" t="n"/>
+      <c r="Z41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="Y42" s="10" t="n"/>
+      <c r="Z42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="Y43" s="10" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="Y44" s="10" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="Y45" s="10" t="n"/>
+      <c r="Z45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="Y47" s="10" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="Y48" s="10" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="Y82" s="10" t="n"/>
+      <c r="Z82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="Y86" s="10" t="n"/>
+      <c r="Z86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="Y88" s="10" t="n"/>
+      <c r="Z88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="Y89" s="10" t="n"/>
+      <c r="Z89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="Y92" s="10" t="n"/>
+      <c r="Z92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="Y95" s="10" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="Y98" s="10" t="n"/>
+      <c r="Z98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="Y101" s="10" t="n"/>
+      <c r="Z101" s="10" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -725,150 +1158,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Question Bank Bulk Upload — Excel Template</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr"/>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>School Question Bank – Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Required columns</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Chapter No, Question Type, Marks, Cognitive Level, Difficulty, and at least one of English Question / Assamese Question.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>School Course only. JNVST is not changed by these fields.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>English Question and Assamese Question belong to the SAME question row. Fill one or both.</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>MCQ / Short / Long</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Image Required</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YES if the question requires a diagram, graph, figure, construction, visual pattern, or other image. Otherwise NO.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Language is detected automatically: English only → ENGLISH; Assamese only → ASSAMESE; both → BOTH.</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge / Understanding / Application / HOTS</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Image Description</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Briefly describe the required image, e.g. "Triangle ABC with AB = 5 cm and AC = 7 cm".</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Question Paper Generator: English / Assamese / Both Medium. Both Medium prints both versions under the same serial number.</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Easy / Medium / Hard</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Image upload</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Excel upload does not upload the image. Teacher can upload the actual image later in Edit Question.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Do not create separate rows for the English and Assamese versions of the same question.</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Use Option A-D columns and Correct Answer as A/B/C/D. For Short/Long, leave option columns blank.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Variation Group</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Use the same value for deliberate variations of the same underlying question pattern.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Bilingual</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Fill English and/or Assamese columns. When generating the paper, the teacher chooses English, Assamese, or Both.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Chapter</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Chapter No must match a chapter already in the Question Bank, or use the dashboard option to create missing chapters with a Chapter Name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Do not rename headers</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Keep the first-row headers unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Mathematics in Excel</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Write LaTeX directly in question/option/explanation cells, e.g. \frac{3}{4}, x^2, \sqrt{25}, \times, \div. You may also use $...$ or \(...\). The importer converts it for MathJax rendering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Text_Book</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>YES if the question is taken from the textbook; NO otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Textbook_Reference</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Optional source details, e.g. NCERT Class 8, Chapter 3, Exercise 3.2, Question 5, page 62.</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>English and Assamese versions go in the same row.</t>
         </is>
       </c>
     </row>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -10,9 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question Bank Bulk" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Question Bank Bulk'!$A$1:$Z$101</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -41,7 +39,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -53,18 +51,8 @@
         <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -72,16 +60,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00D9E2F3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -107,11 +90,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,166 +455,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Subchapter No</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>English Question</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Assamese Question</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="T1" s="9" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Variation Group</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Lesson / Topic</t>
         </is>
       </c>
-      <c r="V1" s="9" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Fixed Question</t>
         </is>
       </c>
-      <c r="W1" s="9" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Text_Book</t>
         </is>
       </c>
-      <c r="X1" s="9" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Textbook_Reference</t>
-        </is>
-      </c>
-      <c r="Y1" s="9" t="inlineStr">
-        <is>
-          <t>Image Required</t>
-        </is>
-      </c>
-      <c r="Z1" s="9" t="inlineStr">
-        <is>
-          <t>Image Description</t>
         </is>
       </c>
     </row>
@@ -747,407 +713,8 @@
           <t>NCERT Class 6, Ch 7, Ex 7.1, Q3</t>
         </is>
       </c>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-    </row>
-    <row r="3">
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-    </row>
-    <row r="4">
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-    </row>
-    <row r="5">
-      <c r="Y5" s="10" t="n"/>
-      <c r="Z5" s="10" t="n"/>
-    </row>
-    <row r="6">
-      <c r="Y6" s="10" t="n"/>
-      <c r="Z6" s="10" t="n"/>
-    </row>
-    <row r="7">
-      <c r="Y7" s="10" t="n"/>
-      <c r="Z7" s="10" t="n"/>
-    </row>
-    <row r="8">
-      <c r="Y8" s="10" t="n"/>
-      <c r="Z8" s="10" t="n"/>
-    </row>
-    <row r="9">
-      <c r="Y9" s="10" t="n"/>
-      <c r="Z9" s="10" t="n"/>
-    </row>
-    <row r="10">
-      <c r="Y10" s="10" t="n"/>
-      <c r="Z10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="Y11" s="10" t="n"/>
-      <c r="Z11" s="10" t="n"/>
-    </row>
-    <row r="12">
-      <c r="Y12" s="10" t="n"/>
-      <c r="Z12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="Y13" s="10" t="n"/>
-      <c r="Z13" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="Y14" s="10" t="n"/>
-      <c r="Z14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="Y15" s="10" t="n"/>
-      <c r="Z15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="Y16" s="10" t="n"/>
-      <c r="Z16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="Y17" s="10" t="n"/>
-      <c r="Z17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="Y18" s="10" t="n"/>
-      <c r="Z18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="Y20" s="10" t="n"/>
-      <c r="Z20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="Y21" s="10" t="n"/>
-      <c r="Z21" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="Y22" s="10" t="n"/>
-      <c r="Z22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="Y23" s="10" t="n"/>
-      <c r="Z23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="Y24" s="10" t="n"/>
-      <c r="Z24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="Y25" s="10" t="n"/>
-      <c r="Z25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="Y26" s="10" t="n"/>
-      <c r="Z26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="Y27" s="10" t="n"/>
-      <c r="Z27" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="Y28" s="10" t="n"/>
-      <c r="Z28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="Y29" s="10" t="n"/>
-      <c r="Z29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="Y30" s="10" t="n"/>
-      <c r="Z30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="Y31" s="10" t="n"/>
-      <c r="Z31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="Y32" s="10" t="n"/>
-      <c r="Z32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="Y33" s="10" t="n"/>
-      <c r="Z33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="Y34" s="10" t="n"/>
-      <c r="Z34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="Y35" s="10" t="n"/>
-      <c r="Z35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="Y36" s="10" t="n"/>
-      <c r="Z36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="Y38" s="10" t="n"/>
-      <c r="Z38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="Y39" s="10" t="n"/>
-      <c r="Z39" s="10" t="n"/>
-    </row>
-    <row r="40">
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="Y41" s="10" t="n"/>
-      <c r="Z41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="Y42" s="10" t="n"/>
-      <c r="Z42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="Y44" s="10" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="Y45" s="10" t="n"/>
-      <c r="Z45" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="Y47" s="10" t="n"/>
-      <c r="Z47" s="10" t="n"/>
-    </row>
-    <row r="48">
-      <c r="Y48" s="10" t="n"/>
-      <c r="Z48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="Y49" s="10" t="n"/>
-      <c r="Z49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="Y50" s="10" t="n"/>
-      <c r="Z50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="Y51" s="10" t="n"/>
-      <c r="Z51" s="10" t="n"/>
-    </row>
-    <row r="52">
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-    </row>
-    <row r="53">
-      <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="10" t="n"/>
-    </row>
-    <row r="54">
-      <c r="Y54" s="10" t="n"/>
-      <c r="Z54" s="10" t="n"/>
-    </row>
-    <row r="55">
-      <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="10" t="n"/>
-    </row>
-    <row r="56">
-      <c r="Y56" s="10" t="n"/>
-      <c r="Z56" s="10" t="n"/>
-    </row>
-    <row r="57">
-      <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-    </row>
-    <row r="59">
-      <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="Y60" s="10" t="n"/>
-      <c r="Z60" s="10" t="n"/>
-    </row>
-    <row r="61">
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-    </row>
-    <row r="62">
-      <c r="Y62" s="10" t="n"/>
-      <c r="Z62" s="10" t="n"/>
-    </row>
-    <row r="63">
-      <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="10" t="n"/>
-    </row>
-    <row r="64">
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-    </row>
-    <row r="65">
-      <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="10" t="n"/>
-    </row>
-    <row r="66">
-      <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-    </row>
-    <row r="68">
-      <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
-    </row>
-    <row r="69">
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-    </row>
-    <row r="70">
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-    </row>
-    <row r="71">
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-    </row>
-    <row r="72">
-      <c r="Y72" s="10" t="n"/>
-      <c r="Z72" s="10" t="n"/>
-    </row>
-    <row r="73">
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-    </row>
-    <row r="74">
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-    </row>
-    <row r="75">
-      <c r="Y75" s="10" t="n"/>
-      <c r="Z75" s="10" t="n"/>
-    </row>
-    <row r="76">
-      <c r="Y76" s="10" t="n"/>
-      <c r="Z76" s="10" t="n"/>
-    </row>
-    <row r="77">
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-    </row>
-    <row r="78">
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-    </row>
-    <row r="79">
-      <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
-    </row>
-    <row r="80">
-      <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="10" t="n"/>
-    </row>
-    <row r="81">
-      <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-    </row>
-    <row r="82">
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-    </row>
-    <row r="83">
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-    </row>
-    <row r="84">
-      <c r="Y84" s="10" t="n"/>
-      <c r="Z84" s="10" t="n"/>
-    </row>
-    <row r="85">
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-    </row>
-    <row r="86">
-      <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="10" t="n"/>
-    </row>
-    <row r="87">
-      <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="10" t="n"/>
-    </row>
-    <row r="88">
-      <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="10" t="n"/>
-    </row>
-    <row r="89">
-      <c r="Y89" s="10" t="n"/>
-      <c r="Z89" s="10" t="n"/>
-    </row>
-    <row r="90">
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-    </row>
-    <row r="91">
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-    </row>
-    <row r="92">
-      <c r="Y92" s="10" t="n"/>
-      <c r="Z92" s="10" t="n"/>
-    </row>
-    <row r="93">
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-    </row>
-    <row r="94">
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-    </row>
-    <row r="95">
-      <c r="Y95" s="10" t="n"/>
-      <c r="Z95" s="10" t="n"/>
-    </row>
-    <row r="96">
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-    </row>
-    <row r="97">
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-    </row>
-    <row r="98">
-      <c r="Y98" s="10" t="n"/>
-      <c r="Z98" s="10" t="n"/>
-    </row>
-    <row r="99">
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-    </row>
-    <row r="100">
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-    </row>
-    <row r="101">
-      <c r="Y101" s="10" t="n"/>
-      <c r="Z101" s="10" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1158,90 +725,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>School Question Bank – Bulk Upload</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="n"/>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Question Bank Bulk Upload — Excel Template</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>School Course only. JNVST is not changed by these fields.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Required columns</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Chapter No, Question Type, Marks, Cognitive Level, Difficulty, and at least one of English Question / Assamese Question.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Image Required</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>YES if the question requires a diagram, graph, figure, construction, visual pattern, or other image. Otherwise NO.</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>English Question and Assamese Question belong to the SAME question row. Fill one or both.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>MCQ / Short / Long</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Image Description</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Briefly describe the required image, e.g. "Triangle ABC with AB = 5 cm and AC = 7 cm".</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Language is detected automatically: English only → ENGLISH; Assamese only → ASSAMESE; both → BOTH.</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge / Understanding / Application / HOTS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Image upload</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Excel upload does not upload the image. Teacher can upload the actual image later in Edit Question.</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Question Paper Generator: English / Assamese / Both Medium. Both Medium prints both versions under the same serial number.</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Easy / Medium / Hard</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Variation Group</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Use the same value for deliberate variations of the same underlying question pattern.</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Do not create separate rows for the English and Assamese versions of the same question.</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Use Option A-D columns and Correct Answer as A/B/C/D. For Short/Long, leave option columns blank.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Bilingual</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>English and Assamese versions go in the same row.</t>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Fill English and/or Assamese columns. When generating the paper, the teacher chooses English, Assamese, or Both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Chapter</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Chapter No must match a chapter already in the Question Bank, or use the dashboard option to create missing chapters with a Chapter Name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Do not rename headers</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Keep the first-row headers unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mathematics in Excel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Write LaTeX directly in question/option/explanation cells, e.g. \frac{3}{4}, x^2, \sqrt{25}, \times, \div. You may also use $...$ or \(...\). The importer converts it for MathJax rendering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Text_Book</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>YES if the question is taken from the textbook; NO otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Textbook_Reference</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optional source details, e.g. NCERT Class 8, Chapter 3, Exercise 3.2, Question 5, page 62.</t>
         </is>
       </c>
     </row>

--- a/Question_Bank_Bulk_Excel_Template.xlsx
+++ b/Question_Bank_Bulk_Excel_Template.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -524,117 +524,122 @@
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>English Question</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Assamese Question</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="T1" s="9" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>Variation Group</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>Lesson / Topic</t>
         </is>
       </c>
-      <c r="V1" s="9" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>Fixed Question</t>
         </is>
       </c>
-      <c r="W1" s="9" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>Text_Book</t>
         </is>
       </c>
-      <c r="X1" s="9" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>Textbook_Reference</t>
         </is>
       </c>
-      <c r="Y1" s="9" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>Image Required</t>
         </is>
       </c>
-      <c r="Z1" s="9" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>Image Description</t>
         </is>
@@ -651,500 +656,505 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Find the value of \frac{3}{4}+\frac{1}{2}.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2 + 2 কিমান?</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Correct answer is 4.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Example: Addition of Unlike Fractions</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>NCERT Class 6, Ch 7, Ex 7.1, Q3</t>
         </is>
       </c>
-      <c r="Y2" s="10" t="n"/>
       <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="Y3" s="10" t="n"/>
       <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="Y4" s="10" t="n"/>
       <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="Y5" s="10" t="n"/>
       <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="Y6" s="10" t="n"/>
       <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="Y7" s="10" t="n"/>
       <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="Y8" s="10" t="n"/>
       <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="Y9" s="10" t="n"/>
       <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="Y10" s="10" t="n"/>
       <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="Y11" s="10" t="n"/>
       <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="Y12" s="10" t="n"/>
       <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="Y13" s="10" t="n"/>
       <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="Y14" s="10" t="n"/>
       <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="Y15" s="10" t="n"/>
       <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="Y16" s="10" t="n"/>
       <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="Y17" s="10" t="n"/>
       <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="Y18" s="10" t="n"/>
       <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="Y19" s="10" t="n"/>
       <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="Y20" s="10" t="n"/>
       <c r="Z20" s="10" t="n"/>
+      <c r="AA20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="Y21" s="10" t="n"/>
       <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="Y22" s="10" t="n"/>
       <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="Y23" s="10" t="n"/>
       <c r="Z23" s="10" t="n"/>
+      <c r="AA23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="Y24" s="10" t="n"/>
       <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="Y25" s="10" t="n"/>
       <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="Y26" s="10" t="n"/>
       <c r="Z26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="Y27" s="10" t="n"/>
       <c r="Z27" s="10" t="n"/>
+      <c r="AA27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="Y28" s="10" t="n"/>
       <c r="Z28" s="10" t="n"/>
+      <c r="AA28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="Y29" s="10" t="n"/>
       <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="Y30" s="10" t="n"/>
       <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="Y31" s="10" t="n"/>
       <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="Y33" s="10" t="n"/>
       <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="Y34" s="10" t="n"/>
       <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="Y35" s="10" t="n"/>
       <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
     </row>
     <row r="36">
-      <c r="Y36" s="10" t="n"/>
       <c r="Z36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="Y37" s="10" t="n"/>
       <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="Y38" s="10" t="n"/>
       <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="Y39" s="10" t="n"/>
       <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="Y40" s="10" t="n"/>
       <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="Y41" s="10" t="n"/>
       <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="Y42" s="10" t="n"/>
       <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="Y43" s="10" t="n"/>
       <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="Y44" s="10" t="n"/>
       <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="Y45" s="10" t="n"/>
       <c r="Z45" s="10" t="n"/>
+      <c r="AA45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="Y46" s="10" t="n"/>
       <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="Y47" s="10" t="n"/>
       <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="Y48" s="10" t="n"/>
       <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="Y49" s="10" t="n"/>
       <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="Y50" s="10" t="n"/>
       <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="Y51" s="10" t="n"/>
       <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="Y53" s="10" t="n"/>
       <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
     </row>
     <row r="54">
-      <c r="Y54" s="10" t="n"/>
       <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
     </row>
     <row r="55">
-      <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
     </row>
     <row r="56">
-      <c r="Y56" s="10" t="n"/>
       <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
     </row>
     <row r="57">
-      <c r="Y57" s="10" t="n"/>
       <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
     </row>
     <row r="58">
-      <c r="Y58" s="10" t="n"/>
       <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="Y59" s="10" t="n"/>
       <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
     </row>
     <row r="60">
-      <c r="Y60" s="10" t="n"/>
       <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
     </row>
     <row r="61">
-      <c r="Y61" s="10" t="n"/>
       <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
     </row>
     <row r="62">
-      <c r="Y62" s="10" t="n"/>
       <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
     </row>
     <row r="63">
-      <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
     </row>
     <row r="64">
-      <c r="Y64" s="10" t="n"/>
       <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
     </row>
     <row r="65">
-      <c r="Y65" s="10" t="n"/>
       <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
     </row>
     <row r="66">
-      <c r="Y66" s="10" t="n"/>
       <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
     </row>
     <row r="67">
-      <c r="Y67" s="10" t="n"/>
       <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
     </row>
     <row r="68">
-      <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
     </row>
     <row r="69">
-      <c r="Y69" s="10" t="n"/>
       <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
     </row>
     <row r="70">
-      <c r="Y70" s="10" t="n"/>
       <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
     </row>
     <row r="71">
-      <c r="Y71" s="10" t="n"/>
       <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
     </row>
     <row r="72">
-      <c r="Y72" s="10" t="n"/>
       <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
     </row>
     <row r="73">
-      <c r="Y73" s="10" t="n"/>
       <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
     </row>
     <row r="74">
-      <c r="Y74" s="10" t="n"/>
       <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
     </row>
     <row r="75">
-      <c r="Y75" s="10" t="n"/>
       <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
     </row>
     <row r="76">
-      <c r="Y76" s="10" t="n"/>
       <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
     </row>
     <row r="77">
-      <c r="Y77" s="10" t="n"/>
       <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
     </row>
     <row r="78">
-      <c r="Y78" s="10" t="n"/>
       <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
     </row>
     <row r="79">
-      <c r="Y79" s="10" t="n"/>
       <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
     </row>
     <row r="80">
-      <c r="Y80" s="10" t="n"/>
       <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
     </row>
     <row r="81">
-      <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
     </row>
     <row r="82">
-      <c r="Y82" s="10" t="n"/>
       <c r="Z82" s="10" t="n"/>
+      <c r="AA82" s="10" t="n"/>
     </row>
     <row r="83">
-      <c r="Y83" s="10" t="n"/>
       <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
     </row>
     <row r="84">
-      <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
     </row>
     <row r="85">
-      <c r="Y85" s="10" t="n"/>
       <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
     </row>
     <row r="86">
-      <c r="Y86" s="10" t="n"/>
       <c r="Z86" s="10" t="n"/>
+      <c r="AA86" s="10" t="n"/>
     </row>
     <row r="87">
-      <c r="Y87" s="10" t="n"/>
       <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
     </row>
     <row r="88">
-      <c r="Y88" s="10" t="n"/>
       <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
     </row>
     <row r="89">
-      <c r="Y89" s="10" t="n"/>
       <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
     </row>
     <row r="90">
-      <c r="Y90" s="10" t="n"/>
       <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
     </row>
     <row r="91">
-      <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
     </row>
     <row r="92">
-      <c r="Y92" s="10" t="n"/>
       <c r="Z92" s="10" t="n"/>
+      <c r="AA92" s="10" t="n"/>
     </row>
     <row r="93">
-      <c r="Y93" s="10" t="n"/>
       <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
     </row>
     <row r="94">
-      <c r="Y94" s="10" t="n"/>
       <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
     </row>
     <row r="95">
-      <c r="Y95" s="10" t="n"/>
       <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
     </row>
     <row r="96">
-      <c r="Y96" s="10" t="n"/>
       <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
     </row>
     <row r="97">
-      <c r="Y97" s="10" t="n"/>
       <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
     </row>
     <row r="98">
-      <c r="Y98" s="10" t="n"/>
       <c r="Z98" s="10" t="n"/>
+      <c r="AA98" s="10" t="n"/>
     </row>
     <row r="99">
-      <c r="Y99" s="10" t="n"/>
       <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
     </row>
     <row r="100">
-      <c r="Y100" s="10" t="n"/>
       <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
     </row>
     <row r="101">
-      <c r="Y101" s="10" t="n"/>
       <c r="Z101" s="10" t="n"/>
+      <c r="AA101" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z101"/>
